--- a/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260803.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260803.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.03%</t>
+          <t>9.93%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>8.67%</t>
+          <t>8.75%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>6.30%</t>
+          <t>6.19%</t>
         </is>
       </c>
     </row>
@@ -677,56 +677,56 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>38,167,000</t>
+          <t>38,327,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.20%</t>
+          <t>5.11%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>184,398,000</t>
+          <t>109,474,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>3.76%</t>
+          <t>3.79%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>109,474,000</t>
+          <t>185,398,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.76%</t>
+          <t>3.65%</t>
         </is>
       </c>
     </row>
@@ -748,117 +748,117 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.68%</t>
+          <t>3.58%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>351,489,964</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.14%</t>
+          <t>3.26%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>202608TX</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>台股期貨</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>2,131</t>
+          <t>26,578,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.14%</t>
+          <t>3.12%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>202608TX</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>華南金</t>
+          <t>台股期貨</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>413,425,000</t>
+          <t>2,131</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.04%</t>
+          <t>3.08%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>26,368,000</t>
+          <t>353,789,964</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>3.03%</t>
+          <t>3.05%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>華南金</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>418,925,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.99%</t>
+          <t>3.01%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.88%</t>
+          <t>2.85%</t>
         </is>
       </c>
     </row>
@@ -902,24 +902,24 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.74%</t>
+          <t>2.72%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>230,616,516</t>
+          <t>25,944,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -931,176 +931,176 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>145,652,000</t>
+          <t>230,616,516</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.57%</t>
+          <t>2.62%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>202,817,000</t>
+          <t>82,118,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.52%</t>
+          <t>2.55%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>131,978,000</t>
+          <t>145,652,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.50%</t>
+          <t>2.52%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>97,142,442</t>
+          <t>202,817,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.48%</t>
+          <t>2.47%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>82,118,000</t>
+          <t>131,978,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.43%</t>
+          <t>2.47%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>25,944,000</t>
+          <t>97,142,442</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.42%</t>
+          <t>2.45%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>99,617,000</t>
+          <t>62,540,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.34%</t>
+          <t>2.40%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>中華電</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>62,540,000</t>
+          <t>99,617,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.20%</t>
+          <t>2.31%</t>
         </is>
       </c>
     </row>
@@ -1122,29 +1122,29 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.08%</t>
+          <t>2.03%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>35,720,000</t>
+          <t>28,550,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>2.02%</t>
+          <t>2.01%</t>
         </is>
       </c>
     </row>
@@ -1173,17 +1173,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>28,550,000</t>
+          <t>186,806,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1210,24 +1210,24 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.99%</t>
+          <t>1.94%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>186,806,000</t>
+          <t>35,720,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.86%</t>
+          <t>1.83%</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.74%</t>
+          <t>1.75%</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>14,098,340,215</t>
+          <t>14,551,766,517</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr"/>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>4,109,989,908</t>
+          <t>3,893,480,308</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr"/>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>-24,837,925</t>
+          <t>-69,308,383</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr"/>
